--- a/artfynd/A 11764-2022 artfynd.xlsx
+++ b/artfynd/A 11764-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11764-2022 artfynd.xlsx
+++ b/artfynd/A 11764-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,6 +1086,236 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126203936</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58509</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Husby S, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>661433</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6559775</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126203951</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58507</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Husby S, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>661433</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6559775</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ida Johansson, Andreas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11764-2022 artfynd.xlsx
+++ b/artfynd/A 11764-2022 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>126203936</v>
       </c>
       <c r="B6" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>126203951</v>
       </c>
       <c r="B7" t="n">
-        <v>58507</v>
+        <v>58511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11764-2022 artfynd.xlsx
+++ b/artfynd/A 11764-2022 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>126203936</v>
       </c>
       <c r="B6" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>126203951</v>
       </c>
       <c r="B7" t="n">
-        <v>58511</v>
+        <v>58514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
